--- a/data/trans_bre/IP1008-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP1008-Estudios-trans_bre.xlsx
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 2,76</t>
+          <t>-3,16; 2,79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,44; 0,0</t>
+          <t>-5,49; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,04</t>
+          <t>0,0; 8,53</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -719,12 +719,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 0,8</t>
+          <t>-0,63; 0,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,09; 1,52</t>
+          <t>0,07; 1,47</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 0,33</t>
+          <t>-2,86; 0,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,88</t>
+          <t>0,0; 3,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 1,44</t>
+          <t>-1,17; 1,49</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 0,48</t>
+          <t>-0,73; 0,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 0,73</t>
+          <t>-0,49; 0,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,07; 1,43</t>
+          <t>0,02; 1,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-83,56; 234,16</t>
+          <t>-79,88; 292,94</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-72,54; 468,07</t>
+          <t>-76,27; 527,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-33,42; 1875,83</t>
+          <t>-14,44; 1713,97</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1008-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP1008-Estudios-trans_bre.xlsx
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 2,79</t>
+          <t>-3,27; 2,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 0,0</t>
+          <t>-4,74; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,53</t>
+          <t>0,0; 8,51</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 0,81</t>
+          <t>-0,44; 0,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 0,78</t>
+          <t>-0,55; 0,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,07; 1,47</t>
+          <t>0,07; 1,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 0,49</t>
+          <t>-2,28; 0,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,42</t>
+          <t>0,0; 2,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 1,49</t>
+          <t>-1,41; 1,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 0,55</t>
+          <t>-0,7; 0,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 0,72</t>
+          <t>-0,48; 0,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,02; 1,36</t>
+          <t>0,04; 1,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-79,88; 292,94</t>
+          <t>-81,84; 233,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-76,27; 527,19</t>
+          <t>-79,42; 435,86</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-14,44; 1713,97</t>
+          <t>-35,51; 1377,3</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1008-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP1008-Estudios-trans_bre.xlsx
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 2,17</t>
+          <t>-3,19; 2,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,74; 0,0</t>
+          <t>-5,44; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,51</t>
+          <t>0,0; 9,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 0,78</t>
+          <t>-0,44; 0,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 0,81</t>
+          <t>-0,55; 0,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,07; 1,57</t>
+          <t>0,09; 1,52</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 0,47</t>
+          <t>-2,63; 0,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,98</t>
+          <t>0,0; 2,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 1,46</t>
+          <t>-1,51; 1,44</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 0,53</t>
+          <t>-0,75; 0,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 0,74</t>
+          <t>-0,47; 0,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,04; 1,38</t>
+          <t>0,07; 1,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-81,84; 233,93</t>
+          <t>-83,56; 234,16</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-79,42; 435,86</t>
+          <t>-72,54; 468,07</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-35,51; 1377,3</t>
+          <t>-33,42; 1875,83</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1008-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP1008-Estudios-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -594,34 +603,24 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-0,13</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-1,55</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2,66</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-8,48%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
+      <c r="C4" s="5" t="n">
+        <v>-0.1320462188689597</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-1.554562778831671</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>2.660024671184061</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>-0.0847646723744287</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
         </is>
       </c>
     </row>
@@ -629,204 +628,116 @@
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-3,19; 2,76</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-5,44; 0,0</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 9,04</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-3.189029744977223</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-5.435313508464374</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="6" t="inlineStr"/>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>2.760308161208117</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>9.044512130875621</v>
+      </c>
+      <c r="F6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>0,04</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0,06</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,6</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>15,32%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>14,34%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>498,58%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-0,44; 0,81</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-0,55; 0,8</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0,09; 1,52</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>0.04464266258718996</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.05731812052633418</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.5997090796608272</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>0.1532061928332559</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.1433873276368414</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>4.985752349418267</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-0,56</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0,87</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-64,77%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-0.4383018150046181</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-0.5545189652183772</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.09216805988481043</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-2,63; 0,33</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,88</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-1,51; 1,44</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.8144084182543677</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.8010984273893893</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>1.517270837799071</v>
+      </c>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -834,77 +745,151 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-0,1</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0,06</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,62</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-16,75%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>13,21%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>238,31%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-0.5562887264403362</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.8723342191332485</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.000686798862342599</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>-0.6476842007389552</v>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.0009462232522944635</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-0,75; 0,48</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-0,47; 0,73</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0,07; 1,43</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-83,56; 234,16</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-72,54; 468,07</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-33,42; 1875,83</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-2.632511593825698</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-1.512861617449017</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr"/>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.3327377364989776</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>2.882721705859641</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>1.441741941587288</v>
+      </c>
+      <c r="F12" s="6" t="inlineStr"/>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-0.09513966173157967</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.05772406852657536</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.6235032650964726</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-0.1674918614251217</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.132075574353072</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>2.383106017031267</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-0.7461576617944544</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-0.4741897906460508</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.07309033073290359</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-0.8356378498656606</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.7254123660459889</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.3342067075180221</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.480026705676073</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.7302528303662963</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>1.425982180308536</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>2.34155536377275</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>4.680673972348274</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>18.75831682807075</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -913,12 +898,12 @@
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
